--- a/ejemplo_taller.xlsx
+++ b/ejemplo_taller.xlsx
@@ -873,7 +873,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>Kia</t>
         </is>
       </c>
       <c r="I10" t="n">
